--- a/docs/sample/MITRE_Sample/UploadSample/acme_sentinel_usecases.xlsx
+++ b/docs/sample/MITRE_Sample/UploadSample/acme_sentinel_usecases.xlsx
@@ -2318,7 +2318,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>T1485 - Data Destruction</t>
+          <t>T1561.001 - Disk Content Wipe</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>T1562.001 - Disable or Modify Tools</t>
+          <t>T1070.004 - File Deletion</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
